--- a/docs/遗物设计.xlsx
+++ b/docs/遗物设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12600"/>
+    <workbookView windowWidth="27930" windowHeight="12615"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,11 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+  <si>
+    <t>是否完成</t>
+  </si>
   <si>
     <t>品质</t>
   </si>
@@ -47,6 +46,9 @@
     <t>补充</t>
   </si>
   <si>
+    <t>完成</t>
+  </si>
+  <si>
     <t>罕见</t>
   </si>
   <si>
@@ -176,7 +178,121 @@
     <t>大铁锚：下回合攻击+1。可叠加，每回合减少1层。</t>
   </si>
   <si>
+    <t>未完成</t>
+  </si>
+  <si>
+    <t>拳击手套·初级</t>
+  </si>
+  <si>
+    <t>每回合开始获得活力1</t>
+  </si>
+  <si>
+    <t>套装：两件-战斗开始时获得力量1，三件-战斗开始时获得力量3</t>
+  </si>
+  <si>
+    <t>拳击手套·中级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得力量1；每回合开始获得活力1</t>
+  </si>
+  <si>
+    <t>拳击手套·高级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得力量2；每回合开始获得活力3</t>
+  </si>
+  <si>
+    <t>速度滑轮·初级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷1；</t>
+  </si>
+  <si>
+    <t>速度滑轮·中级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷2；</t>
+  </si>
+  <si>
+    <t>速度滑轮·高级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷4；</t>
+  </si>
+  <si>
+    <t>大背包</t>
+  </si>
+  <si>
+    <t>战斗开始时能量上限+1；</t>
+  </si>
+  <si>
+    <t>额外电池</t>
+  </si>
+  <si>
+    <t>冷却类人格遗物的CD上限-1；绿油油的步数转换需求降低1/4</t>
+  </si>
+  <si>
+    <t>优雅之羽</t>
+  </si>
+  <si>
+    <t>每当你受到的伤害被格挡时，优雅之羽+1；最多三层。</t>
+  </si>
+  <si>
+    <t>优雅之羽：临时力量+1，如果受到未被格挡的伤害，层数-1；</t>
+  </si>
+  <si>
+    <t>ATM</t>
+  </si>
+  <si>
+    <t>当你使其他玩家获得星光时，目标获得的星光层数+1，自身获得1星光</t>
+  </si>
+  <si>
+    <t>可口糖果</t>
+  </si>
+  <si>
+    <t>打出不低于1费的手牌时，获得 1 层治愈，同时，如果你当前生命为满。则消耗 4 层治愈，获得1能量。</t>
+  </si>
+  <si>
+    <t>维生素</t>
+  </si>
+  <si>
+    <t>你每抽1张牌，获得1治愈。</t>
+  </si>
+  <si>
+    <t>标记喷罐</t>
+  </si>
+  <si>
+    <t>使用技能牌对敌方造成伤害后，对目标施加 1 层标记。</t>
+  </si>
+  <si>
+    <t>魔法箭袋</t>
+  </si>
+  <si>
+    <t>每回合一次，对拥有【标记】的怪物使用技能牌造成伤害时，施加 1 层，复制使用的技能牌并返回手牌。</t>
+  </si>
+  <si>
+    <t>忍术飞镖</t>
+  </si>
+  <si>
+    <t>回合开始时，能量上限 +1。对敌方目标使用技能牌造成伤害时，使怪物额外受到【标记】层数的伤害。</t>
+  </si>
+  <si>
+    <t>手持风扇·小</t>
+  </si>
+  <si>
+    <t>使用人格技能牌后，对随机怪物施加 1 层标记</t>
+  </si>
+  <si>
+    <t>手持风扇·大</t>
+  </si>
+  <si>
+    <t>使用人格技能牌后，抽取一张手牌，并对随机怪物施加 1 层标记</t>
+  </si>
+  <si>
     <t>规定名词：普通（蓝色）对应原版common；罕见（紫色）对应原版uncommon；稀有（金色）对应原版rare；</t>
+  </si>
+  <si>
+    <t>特殊筹码：一般筹码采用token为前缀，特殊筹码采用token_exclusive为前缀，并且统一为金色</t>
   </si>
 </sst>
 </file>
@@ -189,13 +305,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -662,141 +784,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1110,242 +1241,585 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="3" width="12.5"/>
+    <col min="2" max="2" width="12.5"/>
+    <col min="3" max="3" width="15.4333333333333" customWidth="1"/>
     <col min="4" max="4" width="66.1833333333333" customWidth="1"/>
     <col min="5" max="5" width="44.2416666666667" customWidth="1"/>
     <col min="6" max="16" width="12.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5">
-      <c r="B1" t="s">
+    <row r="1" ht="16.5" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="27" spans="2:4">
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="6" ht="33" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="9" ht="16.5" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="13" ht="16.5" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D15" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D17" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+      <c r="D19" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
+      <c r="A25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:5">
+      <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:5">
+      <c r="A27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:5">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:5">
+      <c r="A29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:5">
+      <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:5">
+      <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:5">
+      <c r="A32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:5">
+      <c r="A33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:5">
+      <c r="A34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:5">
+      <c r="A35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:5">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:5">
+      <c r="A37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/遗物设计.xlsx
+++ b/docs/遗物设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12615"/>
+    <workbookView windowWidth="27945" windowHeight="12600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
   <si>
     <t>是否完成</t>
   </si>
@@ -37,6 +37,9 @@
     <t>品质</t>
   </si>
   <si>
+    <t>流派</t>
+  </si>
+  <si>
     <t>中文本地化</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>罕见</t>
   </si>
   <si>
+    <t>基础</t>
+  </si>
+  <si>
     <t>肾上腺素·一般</t>
   </si>
   <si>
@@ -70,6 +76,9 @@
     <t>普通</t>
   </si>
   <si>
+    <t>星光</t>
+  </si>
+  <si>
     <t>手电筒·一般</t>
   </si>
   <si>
@@ -97,6 +106,9 @@
     <t>回合结束时，如果自己手牌少于 5 张，下回合额外获得1张卡牌。</t>
   </si>
   <si>
+    <t>治愈</t>
+  </si>
+  <si>
     <t>缓冲盾牌</t>
   </si>
   <si>
@@ -151,6 +163,9 @@
     <t>生命值为满时，力量+4，且你的技能卡造成的伤害额外上升治愈层数的攻击力。</t>
   </si>
   <si>
+    <t>标记</t>
+  </si>
+  <si>
     <t>普通瞄具</t>
   </si>
   <si>
@@ -178,9 +193,6 @@
     <t>大铁锚：下回合攻击+1。可叠加，每回合减少1层。</t>
   </si>
   <si>
-    <t>未完成</t>
-  </si>
-  <si>
     <t>拳击手套·初级</t>
   </si>
   <si>
@@ -230,6 +242,9 @@
   </si>
   <si>
     <t>冷却类人格遗物的CD上限-1；绿油油的步数转换需求降低1/4</t>
+  </si>
+  <si>
+    <t>闪避</t>
   </si>
   <si>
     <t>优雅之羽</t>
@@ -305,7 +320,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,8 +329,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -464,12 +486,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -784,76 +818,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -862,10 +890,10 @@
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -874,10 +902,10 @@
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,10 +914,10 @@
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -898,10 +926,10 @@
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -910,24 +938,33 @@
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1241,17 +1278,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="12.5"/>
     <col min="3" max="3" width="15.4333333333333" customWidth="1"/>
-    <col min="4" max="4" width="66.1833333333333" customWidth="1"/>
-    <col min="5" max="5" width="44.2416666666667" customWidth="1"/>
-    <col min="6" max="16" width="12.5"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="5" max="5" width="60.125" customWidth="1"/>
+    <col min="6" max="6" width="72.5" customWidth="1"/>
+    <col min="7" max="16" width="12.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" ht="42" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1267,559 +1305,660 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" ht="40.5" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" ht="40.5" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" ht="20.25" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" ht="33" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="60.75" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="6" ht="60.75" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" ht="40.5" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" ht="40.5" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="9" ht="40.5" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" ht="40.5" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="40.5" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" ht="40.5" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
+    </row>
+    <row r="13" ht="40.5" spans="1:6">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" ht="40.5" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="40.5" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" ht="20.25" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" ht="40.5" spans="1:6">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E17" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="2" t="s">
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" ht="40.5" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>12</v>
+      <c r="E18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" ht="20.25" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="40.5" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="40.5" spans="1:6">
+      <c r="A21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" ht="40.5" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" ht="40.5" spans="1:6">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" ht="40.5" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" ht="40.5" spans="1:6">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" ht="20.25" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" ht="40.5" spans="1:6">
+      <c r="A27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" ht="40.5" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" ht="40.5" spans="1:6">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" ht="40.5" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" ht="20.25" spans="1:6">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" ht="20.25" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" ht="40.5" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" ht="40.5" spans="1:6">
       <c r="A34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:5">
-      <c r="A35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" ht="20.25" spans="1:6">
+      <c r="A35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" ht="40.5" spans="1:6">
       <c r="A36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:5">
-      <c r="A37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>87</v>
+        <v>6</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/遗物设计.xlsx
+++ b/docs/遗物设计.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="153">
   <si>
     <t>是否完成</t>
   </si>
@@ -40,6 +40,9 @@
     <t>流派</t>
   </si>
   <si>
+    <t>系列</t>
+  </si>
+  <si>
     <t>中文本地化</t>
   </si>
   <si>
@@ -58,6 +61,9 @@
     <t>基础</t>
   </si>
   <si>
+    <t>核心</t>
+  </si>
+  <si>
     <t>肾上腺素·一般</t>
   </si>
   <si>
@@ -184,6 +190,126 @@
     <t>你的攻击卡造成的伤害+1 ，回合开始时，对随机怪物施加 1 层标记。</t>
   </si>
   <si>
+    <t>拳击手套·初级</t>
+  </si>
+  <si>
+    <t>每回合开始获得活力1</t>
+  </si>
+  <si>
+    <t>套装：两件-战斗开始时获得力量1，三件-战斗开始时获得力量3</t>
+  </si>
+  <si>
+    <t>拳击手套·中级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得力量1；每回合开始获得活力1</t>
+  </si>
+  <si>
+    <t>拳击手套·高级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得力量2；每回合开始获得活力3</t>
+  </si>
+  <si>
+    <t>速度滑轮·初级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷1；</t>
+  </si>
+  <si>
+    <t>速度滑轮·中级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷2；</t>
+  </si>
+  <si>
+    <t>速度滑轮·高级</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷4；</t>
+  </si>
+  <si>
+    <t>大背包</t>
+  </si>
+  <si>
+    <t>战斗开始时能量上限+1；</t>
+  </si>
+  <si>
+    <t>额外电池</t>
+  </si>
+  <si>
+    <t>冷却类人格遗物的CD上限-1；绿油油的步数转换需求降低1/4</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>优雅之羽</t>
+  </si>
+  <si>
+    <t>每当你受到的伤害被格挡时，优雅之羽+1；最多三层。</t>
+  </si>
+  <si>
+    <t>优雅之羽：临时力量+1，如果受到未被格挡的伤害，层数-1；</t>
+  </si>
+  <si>
+    <t>ATM</t>
+  </si>
+  <si>
+    <t>当你使其他玩家获得星光时，目标获得的星光层数+1，自身获得1星光</t>
+  </si>
+  <si>
+    <t>可口糖果</t>
+  </si>
+  <si>
+    <t>打出不低于1费的手牌时，获得 1 层治愈，同时，如果你当前生命为满。则消耗 4 层治愈，获得1能量。</t>
+  </si>
+  <si>
+    <t>维生素</t>
+  </si>
+  <si>
+    <t>你每抽1张牌，获得1治愈。</t>
+  </si>
+  <si>
+    <t>标记喷罐</t>
+  </si>
+  <si>
+    <t>使用技能牌对敌方造成伤害后，对目标施加 1 层标记。</t>
+  </si>
+  <si>
+    <t>魔法箭袋</t>
+  </si>
+  <si>
+    <t>每回合一次，对拥有【标记】的怪物使用技能牌造成伤害时，施加 1 层，复制使用的技能牌并返回手牌。</t>
+  </si>
+  <si>
+    <t>忍术飞镖</t>
+  </si>
+  <si>
+    <t>回合开始时，能量上限 +1。对敌方目标使用技能牌造成伤害时，使怪物额外受到【标记】层数的伤害。</t>
+  </si>
+  <si>
+    <t>手持风扇·小</t>
+  </si>
+  <si>
+    <t>使用人格技能牌后，对随机怪物施加 1 层标记</t>
+  </si>
+  <si>
+    <t>手持风扇·大</t>
+  </si>
+  <si>
+    <t>使用人格技能牌后，抽取一张手牌，并对随机怪物施加 1 层标记</t>
+  </si>
+  <si>
+    <t>需要修改</t>
+  </si>
+  <si>
+    <t>特殊筹码</t>
+  </si>
+  <si>
+    <t>梦想号</t>
+  </si>
+  <si>
     <t>大铁锚</t>
   </si>
   <si>
@@ -193,121 +319,285 @@
     <t>大铁锚：下回合攻击+1。可叠加，每回合减少1层。</t>
   </si>
   <si>
-    <t>拳击手套·初级</t>
-  </si>
-  <si>
-    <t>每回合开始获得活力1</t>
-  </si>
-  <si>
-    <t>套装：两件-战斗开始时获得力量1，三件-战斗开始时获得力量3</t>
-  </si>
-  <si>
-    <t>拳击手套·中级</t>
-  </si>
-  <si>
-    <t>战斗开始时获得力量1；每回合开始获得活力1</t>
-  </si>
-  <si>
-    <t>拳击手套·高级</t>
-  </si>
-  <si>
-    <t>战斗开始时获得力量2；每回合开始获得活力3</t>
-  </si>
-  <si>
-    <t>速度滑轮·初级</t>
-  </si>
-  <si>
-    <t>战斗开始时获得敏捷1；</t>
-  </si>
-  <si>
-    <t>速度滑轮·中级</t>
-  </si>
-  <si>
-    <t>战斗开始时获得敏捷2；</t>
-  </si>
-  <si>
-    <t>速度滑轮·高级</t>
-  </si>
-  <si>
-    <t>战斗开始时获得敏捷4；</t>
-  </si>
-  <si>
-    <t>大背包</t>
-  </si>
-  <si>
-    <t>战斗开始时能量上限+1；</t>
-  </si>
-  <si>
-    <t>额外电池</t>
-  </si>
-  <si>
-    <t>冷却类人格遗物的CD上限-1；绿油油的步数转换需求降低1/4</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>优雅之羽</t>
-  </si>
-  <si>
-    <t>每当你受到的伤害被格挡时，优雅之羽+1；最多三层。</t>
-  </si>
-  <si>
-    <t>优雅之羽：临时力量+1，如果受到未被格挡的伤害，层数-1；</t>
-  </si>
-  <si>
-    <t>ATM</t>
-  </si>
-  <si>
-    <t>当你使其他玩家获得星光时，目标获得的星光层数+1，自身获得1星光</t>
-  </si>
-  <si>
-    <t>可口糖果</t>
-  </si>
-  <si>
-    <t>打出不低于1费的手牌时，获得 1 层治愈，同时，如果你当前生命为满。则消耗 4 层治愈，获得1能量。</t>
-  </si>
-  <si>
-    <t>维生素</t>
-  </si>
-  <si>
-    <t>你每抽1张牌，获得1治愈。</t>
-  </si>
-  <si>
-    <t>标记喷罐</t>
-  </si>
-  <si>
-    <t>使用技能牌对敌方造成伤害后，对目标施加 1 层标记。</t>
-  </si>
-  <si>
-    <t>魔法箭袋</t>
-  </si>
-  <si>
-    <t>每回合一次，对拥有【标记】的怪物使用技能牌造成伤害时，施加 1 层，复制使用的技能牌并返回手牌。</t>
-  </si>
-  <si>
-    <t>忍术飞镖</t>
-  </si>
-  <si>
-    <t>回合开始时，能量上限 +1。对敌方目标使用技能牌造成伤害时，使怪物额外受到【标记】层数的伤害。</t>
-  </si>
-  <si>
-    <t>手持风扇·小</t>
-  </si>
-  <si>
-    <t>使用人格技能牌后，对随机怪物施加 1 层标记</t>
-  </si>
-  <si>
-    <t>手持风扇·大</t>
-  </si>
-  <si>
-    <t>使用人格技能牌后，抽取一张手牌，并对随机怪物施加 1 层标记</t>
+    <t>未完成</t>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>你使用人格技能牌后，使一名没有【强化·三叉戟】的玩家获得【强化·三叉戟】</t>
+  </si>
+  <si>
+    <t>强化·三叉戟：不可叠加；获得1层力量，1层敏捷；</t>
+  </si>
+  <si>
+    <t>梦想号模型</t>
+  </si>
+  <si>
+    <t>战斗开始时获得敏捷2；你每打出15张牌，人格遗物冷却-1；</t>
+  </si>
+  <si>
+    <t>御魂庆典</t>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+  </si>
+  <si>
+    <t>战斗开始时获得99层脆弱[FRAIL_POWER]；第一回合和每3的倍数回合，获得等于诅咒之剑层数的活力；每击倒一个怪物，诅咒之剑获得一层计数。</t>
+  </si>
+  <si>
+    <t>复仇之戟</t>
+  </si>
+  <si>
+    <t>如果你拥有防御损失类debuff，临时力量+5；如果你拥有血量损失类debuff，临时敏捷+5.</t>
+  </si>
+  <si>
+    <r>
+      <t>防御损失类：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">脆弱[FRAIL_POWER]、易伤、遭到包围[SURROUNDED_POWER]、柔嫩[TENDER_POWER]、幽魂形态[WRAITH_FORM_POWER]、敏捷为负数时
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>血量损失类：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紧缠[CONSTRICT_POWER]、瓦解[DISINTEGRATION_POWER]、灾厄。中毒、紧缠[CONSTRICT_POWER]、魔法炸弹[MAGIC_BOMB_POWER]</t>
+    </r>
+  </si>
+  <si>
+    <t>贯穿之铳</t>
+  </si>
+  <si>
+    <t>你的技能牌造成伤害时，将消除目标护盾。</t>
+  </si>
+  <si>
+    <t>先消除护盾，后造成伤害</t>
+  </si>
+  <si>
+    <t>水乡古镇</t>
+  </si>
+  <si>
+    <t>大铜锣</t>
+  </si>
+  <si>
+    <t>你使用人格技能牌后，所有玩家获得1层【强化·大铜锣】</t>
+  </si>
+  <si>
+    <t>强化·大铜锣：获得1层临时力量，1层临时幻影·逆鳞，下回合消失。</t>
+  </si>
+  <si>
+    <t>未设计</t>
+  </si>
+  <si>
+    <t>节日红包</t>
+  </si>
+  <si>
+    <t>魔法学院</t>
+  </si>
+  <si>
+    <t>佐茶蛋糕</t>
+  </si>
+  <si>
+    <t>战斗开始时，获得1层力量。获得后，当前阶段（Act Map）内，打出的攻击牌并对非精英/非boss单位造成伤害时，获得1层【佐茶蛋糕】，回合结束时消除。下一阶段失效。</t>
+  </si>
+  <si>
+    <t>佐茶蛋糕：获得1层临时力量，1层临时敏捷</t>
+  </si>
+  <si>
+    <t>古老法杖</t>
+  </si>
+  <si>
+    <t>所有技能牌造成的伤害+3；战斗开始时，能量上限+1；</t>
+  </si>
+  <si>
+    <t>精品剑盾</t>
+  </si>
+  <si>
+    <t>战斗开始时获得力量2；每回合开始获得活力2；如果是boss房间，每回合获得1层【问题学生】；当你拥有【问题学生】时，敏捷+4；</t>
+  </si>
+  <si>
+    <t>问题学生：不可叠加，受到伤害+2。此buff在受到boss攻击后自动消除。</t>
+  </si>
+  <si>
+    <t>龙宫游乐园</t>
+  </si>
+  <si>
+    <t>惊涛御守</t>
+  </si>
+  <si>
+    <t>使用技能牌时，获得1层灾厄；抽牌时，获得1层治愈；</t>
+  </si>
+  <si>
+    <t>迷幻海鲜汤</t>
+  </si>
+  <si>
+    <t>每回合开始时，获得1活力或者6活力。</t>
+  </si>
+  <si>
+    <t>小蛇玩偶</t>
+  </si>
+  <si>
+    <t>每次受到伤害，获得1层逆鳞</t>
+  </si>
+  <si>
+    <r>
+      <t>【逆鳞】修正：受到伤害-2，临时力量+2；回合结束时全部消除。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【反击】修正：受到未被格挡的伤害时，反击（参考荆棘）同等数值+玩家当前力量的伤害；</t>
+    </r>
+  </si>
+  <si>
+    <t>小鲤鱼玩偶</t>
+  </si>
+  <si>
+    <t>使用人格技能牌后，获得1层【反击】。反击后，获得1层【强化·小鲤鱼玩偶】</t>
+  </si>
+  <si>
+    <t>【强化·小鲤鱼玩偶】：力量+1，敏捷+1；</t>
+  </si>
+  <si>
+    <t>无限之蛇</t>
+  </si>
+  <si>
+    <t>每回合，如果手牌低于8张，则将抽牌补到8张；战斗开始时，能量上限+1；</t>
+  </si>
+  <si>
+    <t>交错双鲤</t>
+  </si>
+  <si>
+    <t>每回合开始获得【强化·交错双鲤】；当你获得活力时，如果没有【强化·交错双鲤】，则获得【强化·交错双鲤】</t>
+  </si>
+  <si>
+    <t>【强化·交错双鲤】：获得6点活力，造成伤害时无视敌方格挡，然后消除此buff；</t>
+  </si>
+  <si>
+    <t>幽魂暗巷</t>
+  </si>
+  <si>
+    <t>计时器</t>
+  </si>
+  <si>
+    <t>获得【改造】时，额外获得 1 层。每 2 层【改造】，使自身攻击力+1。</t>
+  </si>
+  <si>
+    <t>套装·幽魂暗巷：如果是精英/boss房间，每回合获得1层【改造】和1层【灾厄】；【改造】：没有实际作用，只描述为赋予灾厄。</t>
+  </si>
+  <si>
+    <t>重生人偶</t>
+  </si>
+  <si>
+    <t>糖果会员证</t>
+  </si>
+  <si>
+    <t>如果手里没有【怪奇糖果机】，添加一张【怪奇糖果机】到手中；</t>
+  </si>
+  <si>
+    <r>
+      <t>【怪奇糖果机】：消耗，保留，0费用，使用后扣除12金币，获得随机一种糖果系列药水；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【糖果·支援口香糖】：指定任意玩家使用，目标恢复6点生命，1能量，移除目标身上的灾厄。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【糖果·能量补充棒】：只能指定拥有【改造】的玩家使用，对目标添加2层改造和灾厄；目标获得临时力量3，临时敏捷2，持续两回合。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【糖果·大聪明软糖】：指定任意玩家使用，抽三张牌，移除目标身上的改造和灾厄。</t>
+    </r>
   </si>
   <si>
     <t>规定名词：普通（蓝色）对应原版common；罕见（紫色）对应原版uncommon；稀有（金色）对应原版rare；</t>
   </si>
   <si>
-    <t>特殊筹码：一般筹码采用token为前缀，特殊筹码采用token_exclusive为前缀，并且统一为金色</t>
+    <t>特殊筹码：一般筹码采用token为前缀，特殊筹码采用token_exclusive为前缀</t>
+  </si>
+  <si>
+    <t>未设计：先不制作</t>
   </si>
 </sst>
 </file>
@@ -320,7 +610,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,9 +620,29 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
@@ -340,6 +650,13 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -692,12 +1009,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -818,154 +1150,193 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1278,18 +1649,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="12.5"/>
-    <col min="3" max="3" width="15.4333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="5" width="60.125" customWidth="1"/>
-    <col min="6" max="6" width="72.5" customWidth="1"/>
-    <col min="7" max="16" width="12.5"/>
+    <col min="2" max="2" width="5.375" customWidth="1"/>
+    <col min="3" max="3" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="7" width="83.875" customWidth="1"/>
+    <col min="8" max="16" width="12.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" spans="1:6">
+    <row r="1" ht="28.5" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1308,657 +1679,1206 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="40.5" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" ht="14.25" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" ht="14.25" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" ht="40.5" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="1:7">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" ht="14.25" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" ht="14.25" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:7">
+      <c r="A13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" ht="20.25" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:7">
+      <c r="A15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:7">
+      <c r="A17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" ht="14.25" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" ht="14.25" spans="1:7">
+      <c r="A19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" ht="14.25" spans="1:7">
+      <c r="A21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" ht="14.25" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" ht="14.25" spans="1:7">
+      <c r="A23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" ht="14.25" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" ht="14.25" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" ht="14.25" spans="1:7">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" ht="14.25" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:7">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="60.75" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="60.75" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" ht="40.5" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" ht="28.5" spans="1:7">
+      <c r="A29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" ht="40.5" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="40.5" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" ht="40.5" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" ht="40.5" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" ht="40.5" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" ht="40.5" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" ht="40.5" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" ht="40.5" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" ht="20.25" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" ht="14.25" spans="1:7">
+      <c r="A30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" ht="14.25" spans="1:7">
+      <c r="A31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" ht="40.5" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" ht="40.5" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" ht="20.25" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" ht="28.5" spans="1:7">
+      <c r="A32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" ht="28.5" spans="1:7">
+      <c r="A33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" ht="14.25" spans="1:7">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" ht="14.25" spans="1:7">
+      <c r="A35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" ht="17.25" spans="1:7">
+      <c r="A36" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" spans="1:7">
+      <c r="A37" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" ht="40.5" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="C37" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" spans="1:7">
+      <c r="A38" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" ht="34.5" spans="1:7">
+      <c r="A39" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" ht="69" spans="1:7">
+      <c r="A40" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" ht="40.5" spans="1:6">
-      <c r="A21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="C40" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" spans="1:7">
+      <c r="A41" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" spans="1:7">
+      <c r="A42" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" spans="1:7">
+      <c r="A43" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" ht="34.5" spans="1:7">
+      <c r="A44" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" spans="1:7">
+      <c r="A45" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" ht="40.5" spans="1:6">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="C45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" ht="34.5" spans="1:7">
+      <c r="A46" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" spans="1:7">
+      <c r="A47" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" ht="17.25" spans="1:7">
+      <c r="A48" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" ht="34.5" spans="1:7">
+      <c r="A49" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" ht="40.5" spans="1:6">
-      <c r="A23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="C49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" spans="1:7">
+      <c r="A50" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" ht="40.5" spans="1:6">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="C50" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" spans="1:7">
+      <c r="A51" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="13"/>
+    </row>
+    <row r="52" ht="34.5" spans="1:7">
+      <c r="A52" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" ht="34.5" spans="1:7">
+      <c r="A53" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" ht="17.25" spans="1:7">
+      <c r="A54" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" ht="40.5" spans="1:6">
-      <c r="A25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" ht="20.25" spans="1:6">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" ht="40.5" spans="1:6">
-      <c r="A27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" ht="40.5" spans="1:6">
-      <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" spans="1:6">
-      <c r="A29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" ht="40.5" spans="1:6">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" ht="20.25" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" ht="20.25" spans="1:6">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" ht="40.5" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" ht="40.5" spans="1:6">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" ht="20.25" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" ht="40.5" spans="1:6">
-      <c r="A36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
+      <c r="C54" s="8" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>92</v>
+      <c r="D54" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" ht="86.25" spans="1:7">
+      <c r="A55" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" ht="20.25" spans="1:5">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+    </row>
+    <row r="57" ht="20.25" spans="1:5">
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+    </row>
+    <row r="58" ht="20.25" spans="1:5">
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+    </row>
+    <row r="59" ht="22.5" spans="1:1">
+      <c r="A59" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" spans="1:1">
+      <c r="A60" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" ht="22.5" spans="1:1">
+      <c r="A61" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
